--- a/AAII_Financials/Quarterly/SAEYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SAEYY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="92">
   <si>
     <t>SAEYY</t>
   </si>
@@ -656,84 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -779,8 +783,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -826,8 +833,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -873,8 +883,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,8 +905,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -939,8 +953,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,8 +1003,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1033,8 +1053,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,8 +1122,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1143,8 +1170,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1190,8 +1220,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,8 +1242,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1256,8 +1290,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1303,8 +1340,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1350,8 +1390,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1397,8 +1440,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1444,8 +1490,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,8 +1540,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1538,8 +1590,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1585,8 +1640,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1740,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,8 +1840,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1820,8 +1890,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1867,8 +1940,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,8 +1990,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1961,60 +2040,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,290 +2137,309 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>87200</v>
+      </c>
+      <c r="E41" s="3">
         <v>106800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>108500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>176400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>111300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>112400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>100300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>110900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>118800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>106500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>93000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>160600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>142100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>106800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>71400</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E42" s="3">
         <v>48900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>130400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>141900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>259400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>87300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>83500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>123200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>129000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>129600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>132600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>86900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>131700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>127900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>121100</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>174600</v>
+      </c>
+      <c r="E43" s="3">
         <v>180300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>179400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>144400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>140000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>125600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>129200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>116700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>103600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>108900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>131900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>143300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>135200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>66000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>43800</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>243700</v>
+      </c>
+      <c r="E44" s="3">
         <v>247700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>251300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>200800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>190000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>174600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>159200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>158800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>143300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>145300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>150100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>135900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>130200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>106300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>106600</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3">
         <v>38200</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>26700</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>32500</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R45" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>628400</v>
+      </c>
+      <c r="E46" s="3">
         <v>667900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>727300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>746000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>781500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>556200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>517700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>575600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>552900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>538900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>552100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>526600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>539200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>407000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>367500</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2342,140 +2447,149 @@
         <v>1700</v>
       </c>
       <c r="E47" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F47" s="3">
         <v>1800</v>
-      </c>
-      <c r="F47" s="3">
-        <v>1700</v>
       </c>
       <c r="G47" s="3">
         <v>1700</v>
       </c>
       <c r="H47" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I47" s="3">
         <v>1500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>5100</v>
       </c>
       <c r="L47" s="3">
         <v>5100</v>
       </c>
       <c r="M47" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N47" s="3">
         <v>1500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4000</v>
-      </c>
-      <c r="P47" s="3">
-        <v>1400</v>
       </c>
       <c r="Q47" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>235800</v>
+      </c>
+      <c r="E48" s="3">
         <v>229000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>223900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>199100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>188100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>97500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>85500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>90000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>89400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>90600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>96100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>98600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>104200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>93300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>91300</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>442700</v>
+      </c>
+      <c r="E49" s="3">
         <v>449600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>462000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>472500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>475200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>440100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>425800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>461900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>448600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>456600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>473200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>529500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>548400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>313700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>308900</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,55 +2685,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E52" s="3">
         <v>8600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6800</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" s="3">
         <v>3800</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q52" s="3">
         <v>10200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2785,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1319100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1358700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1425700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1431200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1458700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1104300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1038700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1136500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1098400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1093100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1129200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1159000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1197300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>825700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>779600</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,243 +2877,259 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>288100</v>
+      </c>
+      <c r="E57" s="3">
         <v>321300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>291200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>269400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>288500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>229900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>181500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>202100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>189600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>173200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>168000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>171000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>178700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>108600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>73700</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E58" s="3">
         <v>26500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>101300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>103600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>91700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10600</v>
-      </c>
-      <c r="I58" s="3">
-        <v>10000</v>
       </c>
       <c r="J58" s="3">
         <v>10000</v>
       </c>
       <c r="K58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L58" s="3">
         <v>9700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>80700</v>
+      </c>
+      <c r="E59" s="3">
         <v>84600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>70900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>77400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>68700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>59900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>61500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>61100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>56200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>57800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>52600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>396300</v>
+      </c>
+      <c r="E60" s="3">
         <v>432500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>469600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>443900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>457700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>309200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>258500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>272100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>260800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>243700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>247300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>236700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>246500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>169900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>127500</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>377700</v>
+      </c>
+      <c r="E61" s="3">
         <v>382600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>387800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>356800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>360300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>256100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>246000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>261800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>251900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>253300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>259800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>249100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>270300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>270800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>243000</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3026,11 +3172,14 @@
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R62" s="3">
         <v>15600</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,55 +3325,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>776300</v>
+      </c>
+      <c r="E66" s="3">
         <v>818700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>863100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>818800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>837900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>570700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>510700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>540300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>520300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>506600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>519000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>494500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>526300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>448400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>400600</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,55 +3595,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3">
+        <v>-413000</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3">
         <v>-420600</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
         <v>-387700</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>-335700</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-311200</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>-308700</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>-306400</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>-305000</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3795,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>522400</v>
+      </c>
+      <c r="E76" s="3">
         <v>519100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>539200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>589300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>597400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>512200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>501100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>563600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>550200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>555700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>577200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>555800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>559800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>377300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>379000</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,60 +3895,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3805,8 +4000,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,55 +4022,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E83" s="3">
         <v>18200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-22200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>19100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>18300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>17600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-15600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-11200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>10600</v>
-      </c>
-      <c r="O83" s="3">
-        <v>9600</v>
       </c>
       <c r="P83" s="3">
         <v>9600</v>
       </c>
       <c r="Q83" s="3">
+        <v>9600</v>
+      </c>
+      <c r="R83" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4320,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E89" s="3">
         <v>25900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-22100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-23700</v>
       </c>
-      <c r="G89" s="3">
-        <v>38900</v>
-      </c>
       <c r="H89" s="3">
+        <v>39000</v>
+      </c>
+      <c r="I89" s="3">
         <v>39800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-17600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>29400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>22600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>36300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>47800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-31400</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,55 +4392,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-31000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16500</v>
       </c>
-      <c r="G91" s="3">
-        <v>-31300</v>
-      </c>
       <c r="H91" s="3">
+        <v>-31400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-13200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6400</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,55 +4540,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E94" s="3">
         <v>56500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-30200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>89700</v>
       </c>
-      <c r="G94" s="3">
-        <v>-209100</v>
-      </c>
       <c r="H94" s="3">
+        <v>-209000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-21000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>18200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-62400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>33700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-29300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-16500</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4612,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,84 +4810,90 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-82000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-9100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6200</v>
       </c>
-      <c r="G100" s="3">
-        <v>158100</v>
-      </c>
       <c r="H100" s="3">
+        <v>158300</v>
+      </c>
+      <c r="I100" s="3">
         <v>-11200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>27800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>4</v>
@@ -4661,51 +4910,57 @@
       <c r="Q101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-61400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>59700</v>
       </c>
-      <c r="G102" s="3">
-        <v>-12100</v>
-      </c>
       <c r="H102" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="I102" s="3">
         <v>7300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-74700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>22800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>34800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>34300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-51800</v>
       </c>
     </row>
